--- a/website/examples/example_odk_odk_form_launcher.xlsx
+++ b/website/examples/example_odk_odk_form_launcher.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R48c1edbcdc0e4ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rbc96a2232a2d4cb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R05fabe7ceb2342f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rce40c9162d934ced"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R4987ff20694f42e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rad52979027c442ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -468,7 +468,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E2" s="8" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='odk_form_launcher',input_form_selector=${input_form_selector},return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='odk_form_launcher',input_form_selector=${input_form_selector},return_mode='flat')</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -580,10 +580,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str"/>
       <x:c r="E11" s="8" t="str"/>
@@ -593,10 +593,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C12" s="7" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str"/>
       <x:c r="E12" s="8" t="str"/>
@@ -663,7 +663,7 @@
         <x:v>form_id</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
-        <x:v>researchos_odk_form_launcher</x:v>
+        <x:v>methodmesh_odk_form_launcher</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
